--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93418</v>
+        <v>93421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
